--- a/data/trans_orig/IP1007-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1007-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48355</t>
+          <t>48569</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108769</t>
+          <t>109292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103815</t>
+          <t>103823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108209</t>
+          <t>108206</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205229</t>
+          <t>205386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209770</t>
+          <t>209769</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131287</t>
+          <t>132039</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260654</t>
+          <t>260639</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154462</t>
+          <t>154735</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160069</t>
+          <t>159947</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317640</t>
+          <t>317385</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>523</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>676304</t>
+          <t>675877</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>680497</t>
+          <t>680498</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>715706</t>
+          <t>715396</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1394127</t>
+          <t>1394134</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1401446</t>
+          <t>1401359</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50615</t>
+          <t>50007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110853</t>
+          <t>110798</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73252</t>
+          <t>72851</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156347</t>
+          <t>155449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56718</t>
+          <t>56734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112779</t>
+          <t>112754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>701920</t>
+          <t>701444</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>743843</t>
+          <t>744427</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1449347</t>
+          <t>1449237</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1454501</t>
+          <t>1454503</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61270</t>
+          <t>60603</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118441</t>
+          <t>118569</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97524</t>
+          <t>98202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208454</t>
+          <t>208990</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>166168</t>
+          <t>166629</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>330986</t>
+          <t>330951</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>698116</t>
+          <t>698555</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>738921</t>
+          <t>739007</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>744216</t>
+          <t>744220</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1441715</t>
+          <t>1441690</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1448058</t>
+          <t>1448057</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">

--- a/data/trans_orig/IP1007-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1007-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1122</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3999</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4052</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,13%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4379</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3493</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51446</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48569</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48516</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,87%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>92,29%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>168</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109292</t>
+          <t>108406</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,92 +1065,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1842</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4934</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1842</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>547</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>106915</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>103292</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>108209</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>106915</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>103823</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>108206</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>205386</t>
+          <t>204971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209769</t>
+          <t>209772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2207,47 +2207,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,107 +2780,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>725</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>725</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3616</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4226</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3638</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>134930</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>131771</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,14%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>134930</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>132039</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260639</t>
+          <t>260051</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3128,102 +3128,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3519</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>616</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3169</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4789</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4577</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3236,74 +3236,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>163358</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>160539</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>157288</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>154735</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>155105</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,61%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>163358</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>159947</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>492</t>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317385</t>
+          <t>317173</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>7086</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1738</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5144</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5498</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1256</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>7304</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>719432</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>715614</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>721441</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>679283</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>675877</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>680498</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>675523</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>680497</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,74%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>719432</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>715396</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>721444</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2096</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1394134</t>
+          <t>1393826</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1401359</t>
+          <t>1401790</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4045,107 +4045,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>568</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2957</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2977</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2927</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -4158,74 +4158,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52396</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50007</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50608</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,93%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>163</t>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110798</t>
+          <t>110748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4501,47 +4501,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4844,47 +4844,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5074,107 +5074,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4910</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4435</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4467</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4546</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -5187,74 +5187,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76865</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>72851</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>73326</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,3%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>225</t>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155449</t>
+          <t>155528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5530,47 +5530,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5760,107 +5760,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>687</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3439</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3476</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -5873,72 +5873,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59558</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>56698</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59558</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>56734</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112754</t>
+          <t>112791</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6216,47 +6216,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6559,47 +6559,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6789,72 +6789,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3739</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1464</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5484</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5622</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>3715</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6902,74 +6902,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>747455</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>744403</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>705464</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>701444</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>701306</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,79%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>747455</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>744427</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2081</t>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1449237</t>
+          <t>1449308</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7368,107 +7368,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>636</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>636</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3859</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3223</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -7481,72 +7481,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>63826</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61578</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>63826</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>60603</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118569</t>
+          <t>118610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7711,107 +7711,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1163</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5745</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5754</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5918</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1163</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>5240</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -7824,74 +7824,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>102784</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>98202</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>98193</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,88%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,46%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>317</t>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208990</t>
+          <t>208312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8167,47 +8167,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8510,47 +8510,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8853,47 +8853,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9539,47 +9539,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9769,107 +9769,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>1318</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4220</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4779</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1318</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4074</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -9882,72 +9882,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>169531</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>166134</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>169531</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>166629</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>330951</t>
+          <t>330246</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,74 +10112,74 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1163</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5816</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5837</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -10225,74 +10225,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>742891</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>739520</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>744222</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>703208</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>698555</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>698551</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,83%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>99,17%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>742891</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>739007</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>744220</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2122</t>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1441690</t>
+          <t>1441294</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1448057</t>
+          <t>1448519</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
